--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4354"/>
+  <dimension ref="A1:B4377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35256,6 +35256,190 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4355">
+      <c r="A4355" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B4355" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4356">
+      <c r="A4356" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B4356" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4357">
+      <c r="A4357" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B4357" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4358">
+      <c r="A4358" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B4358" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4359">
+      <c r="A4359" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B4359" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4360">
+      <c r="A4360" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B4360" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4361">
+      <c r="A4361" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B4361" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4362">
+      <c r="A4362" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B4362" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4363">
+      <c r="A4363" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B4363" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4364">
+      <c r="A4364" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B4364" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4365">
+      <c r="A4365" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B4365" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4366">
+      <c r="A4366" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B4366" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4367">
+      <c r="A4367" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B4367" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4368">
+      <c r="A4368" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4368" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4369">
+      <c r="A4369" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B4369" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4370">
+      <c r="A4370" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B4370" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4371">
+      <c r="A4371" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B4371" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4372">
+      <c r="A4372" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B4372" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4373">
+      <c r="A4373" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B4373" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4374">
+      <c r="A4374" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B4374" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4375">
+      <c r="A4375" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4375" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4376">
+      <c r="A4376" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B4376" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4377">
+      <c r="A4377" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4377" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
